--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89319</v>
+        <v>89321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93072</v>
+        <v>93075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93072</v>
+        <v>93075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99680</v>
+        <v>99683</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104865</v>
+        <v>104868</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90050</v>
+        <v>90052</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99683</v>
+        <v>99684</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104868</v>
+        <v>104869</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92822</v>
+        <v>92827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89321</v>
+        <v>89323</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>136656758</v>
       </c>
       <c r="B41" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>136656763</v>
       </c>
       <c r="B42" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>136656760</v>
       </c>
       <c r="B43" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136656756</v>
       </c>
       <c r="B54" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136656780</v>
       </c>
       <c r="B55" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99684</v>
+        <v>99689</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90052</v>
+        <v>90054</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89323</v>
+        <v>89325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99689</v>
+        <v>99691</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90054</v>
+        <v>90056</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89325</v>
+        <v>89327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>136656758</v>
       </c>
       <c r="B41" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>136656763</v>
       </c>
       <c r="B42" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>136656760</v>
       </c>
       <c r="B43" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136656756</v>
       </c>
       <c r="B54" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136656780</v>
       </c>
       <c r="B55" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99691</v>
+        <v>99697</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90056</v>
+        <v>90058</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92831</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89327</v>
+        <v>89329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>136656758</v>
       </c>
       <c r="B41" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>136656763</v>
       </c>
       <c r="B42" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>136656760</v>
       </c>
       <c r="B43" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136656756</v>
       </c>
       <c r="B54" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136656780</v>
       </c>
       <c r="B55" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99697</v>
+        <v>99699</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90058</v>
+        <v>90060</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89329</v>
+        <v>89330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>136656758</v>
       </c>
       <c r="B41" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>136656763</v>
       </c>
       <c r="B42" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>136656760</v>
       </c>
       <c r="B43" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136656756</v>
       </c>
       <c r="B54" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136656780</v>
       </c>
       <c r="B55" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99699</v>
+        <v>99700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90060</v>
+        <v>90061</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92834</v>
+        <v>92840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89330</v>
+        <v>89336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99700</v>
+        <v>99706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90061</v>
+        <v>90067</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92840</v>
+        <v>92844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89336</v>
+        <v>89340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>136656758</v>
       </c>
       <c r="B41" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>136656763</v>
       </c>
       <c r="B42" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>136656760</v>
       </c>
       <c r="B43" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136656756</v>
       </c>
       <c r="B54" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136656780</v>
       </c>
       <c r="B55" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99706</v>
+        <v>99710</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90067</v>
+        <v>90071</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99710</v>
+        <v>99712</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92844</v>
+        <v>92846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>136656758</v>
       </c>
       <c r="B41" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>136656763</v>
       </c>
       <c r="B42" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>136656760</v>
       </c>
       <c r="B43" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136656756</v>
       </c>
       <c r="B54" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136656780</v>
       </c>
       <c r="B55" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99712</v>
+        <v>99714</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90071</v>
+        <v>90073</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92846</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89342</v>
+        <v>89355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>136656758</v>
       </c>
       <c r="B41" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>136656763</v>
       </c>
       <c r="B42" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>136656760</v>
       </c>
       <c r="B43" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136656756</v>
       </c>
       <c r="B54" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136656780</v>
       </c>
       <c r="B55" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99714</v>
+        <v>99727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90073</v>
+        <v>90086</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136656772</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136656771</v>
       </c>
       <c r="B6" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136656777</v>
       </c>
       <c r="B7" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136656761</v>
       </c>
       <c r="B8" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>136656765</v>
       </c>
       <c r="B9" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>136656778</v>
       </c>
       <c r="B10" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136656776</v>
       </c>
       <c r="B14" t="n">
-        <v>89355</v>
+        <v>89357</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136656779</v>
       </c>
       <c r="B15" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136656785</v>
       </c>
       <c r="B16" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>136656764</v>
       </c>
       <c r="B17" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>136656769</v>
       </c>
       <c r="B18" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>136656758</v>
       </c>
       <c r="B41" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>136656763</v>
       </c>
       <c r="B42" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>136656760</v>
       </c>
       <c r="B43" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136656756</v>
       </c>
       <c r="B54" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136656780</v>
       </c>
       <c r="B55" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>136656782</v>
       </c>
       <c r="B79" t="n">
-        <v>99727</v>
+        <v>99729</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>136656775</v>
       </c>
       <c r="B82" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>136656770</v>
       </c>
       <c r="B94" t="n">
-        <v>90086</v>
+        <v>90088</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
